--- a/artfynd/A 59519-2025 artfynd.xlsx
+++ b/artfynd/A 59519-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1065,6 +1065,112 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130210298</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98867</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Klockhammar, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>499776</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6581404</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kil</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59519-2025 artfynd.xlsx
+++ b/artfynd/A 59519-2025 artfynd.xlsx
@@ -1070,7 +1070,7 @@
         <v>130210298</v>
       </c>
       <c r="B5" t="n">
-        <v>98867</v>
+        <v>98954</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59519-2025 artfynd.xlsx
+++ b/artfynd/A 59519-2025 artfynd.xlsx
@@ -1070,7 +1070,7 @@
         <v>130210298</v>
       </c>
       <c r="B5" t="n">
-        <v>98954</v>
+        <v>98957</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59519-2025 artfynd.xlsx
+++ b/artfynd/A 59519-2025 artfynd.xlsx
@@ -1070,7 +1070,7 @@
         <v>130210298</v>
       </c>
       <c r="B5" t="n">
-        <v>98957</v>
+        <v>98983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59519-2025 artfynd.xlsx
+++ b/artfynd/A 59519-2025 artfynd.xlsx
@@ -1070,7 +1070,7 @@
         <v>130210298</v>
       </c>
       <c r="B5" t="n">
-        <v>98983</v>
+        <v>98984</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59519-2025 artfynd.xlsx
+++ b/artfynd/A 59519-2025 artfynd.xlsx
@@ -1070,7 +1070,7 @@
         <v>130210298</v>
       </c>
       <c r="B5" t="n">
-        <v>98984</v>
+        <v>98985</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59519-2025 artfynd.xlsx
+++ b/artfynd/A 59519-2025 artfynd.xlsx
@@ -1070,7 +1070,7 @@
         <v>130210298</v>
       </c>
       <c r="B5" t="n">
-        <v>98985</v>
+        <v>98987</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59519-2025 artfynd.xlsx
+++ b/artfynd/A 59519-2025 artfynd.xlsx
@@ -1070,7 +1070,7 @@
         <v>130210298</v>
       </c>
       <c r="B5" t="n">
-        <v>98987</v>
+        <v>98991</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59519-2025 artfynd.xlsx
+++ b/artfynd/A 59519-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>12684</v>
+        <v>129063136</v>
       </c>
       <c r="B2" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,51 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100084</v>
+        <v>4769</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Muscardinus avellanarius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Alkotteberget, Kilsbergen, Nrk</t>
+          <t>Blackstahyttan, Atlasruta 10F6a (Blackstahyttan), Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499720.0538156395</v>
+        <v>499858</v>
       </c>
       <c r="R2" t="n">
-        <v>6581561.006061732</v>
+        <v>6581437</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,27 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2007-09-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2007-09-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Tall/granhygge i sydostsluttning på Alkotteberget med kraftigt uppslag av björk. Snårskikt av Calamagrostis och örnbräken bitvis frodig. Ett fint hanbo 7,5 cm i diameter och placerat 90 cm över marken i tall.</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,18 +757,24 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Boris Berglund</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Boris Berglund</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -809,12 +784,7 @@
         <v>12438</v>
       </c>
       <c r="B3" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56614</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -865,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499743.021526742</v>
+        <v>499743</v>
       </c>
       <c r="R3" t="n">
-        <v>6581481.50254535</v>
+        <v>6581482</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -898,19 +868,9 @@
           <t>2007-09-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2007-10-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -946,15 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124801385</v>
+        <v>12684</v>
       </c>
       <c r="B4" t="n">
-        <v>100451</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56614</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -962,42 +917,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>100084</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Muscardinus avellanarius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rökärret N om, Nrk</t>
+          <t>Alkotteberget, Kilsbergen, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499778</v>
+        <v>499720</v>
       </c>
       <c r="R4" t="n">
-        <v>6581457</v>
+        <v>6581561</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,12 +985,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2007-09-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2007-09-08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Tall/granhygge i sydostsluttning på Alkotteberget med kraftigt uppslag av björk. Snårskikt av Calamagrostis och örnbräken bitvis frodig. Ett fint hanbo 7,5 cm i diameter och placerat 90 cm över marken i tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,29 +1004,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>stig/traktorväg i glänta i gles blandskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Boris Berglund</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Michael Andersson, Madelen Andersson, Jessica Wiener, Mattias Sterner</t>
+          <t>Boris Berglund</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1070,7 +1025,7 @@
         <v>130210298</v>
       </c>
       <c r="B5" t="n">
-        <v>98991</v>
+        <v>99153</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,6 +1125,122 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>124801385</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rökärret N om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>499778</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6581457</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kil</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>stig/traktorväg i glänta i gles blandskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Michael Andersson, Madelen Andersson, Jessica Wiener, Mattias Sterner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59519-2025 artfynd.xlsx
+++ b/artfynd/A 59519-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129063136</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,6 +913,11 @@
           <t>Hasselmusinventering i Örebro län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/12438</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1019,6 +1034,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/12684</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1125,6 +1145,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210298</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1241,8 +1266,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124801385</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>